--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18496,6 +18496,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B789" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C789" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="D789" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E789" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F789" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G789" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18519,6 +18519,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B790" t="n">
+        <v>350</v>
+      </c>
+      <c r="C790" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="D790" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E790" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F790" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G790" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18542,6 +18542,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B791" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C791" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="D791" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E791" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F791" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18565,6 +18565,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B792" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C792" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D792" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E792" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F792" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="G792" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18406,22 +18406,22 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B785" t="n">
-        <v>5600</v>
+        <v>12600</v>
       </c>
       <c r="C785" t="n">
-        <v>2.98000001907349</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="D785" t="n">
-        <v>2.83999991416931</v>
+        <v>2.90000009536743</v>
       </c>
       <c r="E785" t="n">
-        <v>2.96000003814697</v>
+        <v>3</v>
       </c>
       <c r="F785" t="n">
-        <v>2.90000009536743</v>
+        <v>2.94000005722046</v>
       </c>
       <c r="G785" t="s">
         <v>7</v>
@@ -18429,19 +18429,19 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B786" t="n">
-        <v>4900</v>
+        <v>5600</v>
       </c>
       <c r="C786" t="n">
-        <v>2.92000007629395</v>
+        <v>2.98000001907349</v>
       </c>
       <c r="D786" t="n">
-        <v>2.85999989509583</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="E786" t="n">
-        <v>2.92000007629395</v>
+        <v>2.96000003814697</v>
       </c>
       <c r="F786" t="n">
         <v>2.90000009536743</v>
@@ -18452,22 +18452,22 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B787" t="n">
-        <v>700</v>
+        <v>4900</v>
       </c>
       <c r="C787" t="n">
-        <v>2.85999989509583</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="D787" t="n">
         <v>2.85999989509583</v>
       </c>
       <c r="E787" t="n">
-        <v>2.85999989509583</v>
+        <v>2.92000007629395</v>
       </c>
       <c r="F787" t="n">
-        <v>2.85999989509583</v>
+        <v>2.90000009536743</v>
       </c>
       <c r="G787" t="s">
         <v>7</v>
@@ -18475,7 +18475,7 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B788" t="n">
         <v>700</v>
@@ -18498,22 +18498,22 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B789" t="n">
-        <v>1050</v>
+        <v>700</v>
       </c>
       <c r="C789" t="n">
-        <v>2.83999991416931</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="D789" t="n">
-        <v>2.83999991416931</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="E789" t="n">
-        <v>2.83999991416931</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="F789" t="n">
-        <v>2.83999991416931</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="G789" t="s">
         <v>7</v>
@@ -18521,10 +18521,10 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B790" t="n">
-        <v>350</v>
+        <v>1050</v>
       </c>
       <c r="C790" t="n">
         <v>2.83999991416931</v>
@@ -18544,10 +18544,10 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B791" t="n">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="C791" t="n">
         <v>2.83999991416931</v>
@@ -18567,13 +18567,13 @@
     </row>
     <row r="792">
       <c r="A792" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B792" t="n">
-        <v>4200</v>
+        <v>1400</v>
       </c>
       <c r="C792" t="n">
-        <v>2.92000007629395</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="D792" t="n">
         <v>2.83999991416931</v>
@@ -18582,9 +18582,32 @@
         <v>2.83999991416931</v>
       </c>
       <c r="F792" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G792" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B793" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C793" t="n">
         <v>2.92000007629395</v>
       </c>
-      <c r="G792" t="s">
+      <c r="D793" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E793" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F793" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="G793" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18590,24 +18590,47 @@
     </row>
     <row r="793">
       <c r="A793" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B793" t="n">
-        <v>2100</v>
+        <v>4200</v>
       </c>
       <c r="C793" t="n">
         <v>2.92000007629395</v>
       </c>
       <c r="D793" t="n">
-        <v>2.92000007629395</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="E793" t="n">
-        <v>2.92000007629395</v>
+        <v>2.83999991416931</v>
       </c>
       <c r="F793" t="n">
         <v>2.92000007629395</v>
       </c>
       <c r="G793" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B794" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C794" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D794" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E794" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F794" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="G794" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18634,6 +18634,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B795" t="n">
+        <v>0</v>
+      </c>
+      <c r="C795" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D795" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E795" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F795" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="G795" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -21097,6 +21097,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B798" t="n">
+        <v>14350</v>
+      </c>
+      <c r="C798" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D798" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E798" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="F798" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G798" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H798" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -21123,6 +21123,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B799" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C799" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D799" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E799" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F799" t="n">
+        <v>3</v>
+      </c>
+      <c r="G799" t="n">
+        <v>3</v>
+      </c>
+      <c r="H799" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -21201,6 +21201,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B802" t="n">
+        <v>18200</v>
+      </c>
+      <c r="C802" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D802" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="E802" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F802" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G802" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H802" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18864,6 +18864,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>0</v>
+      </c>
+      <c r="C805" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="D805" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E805" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="F805" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18887,6 +18887,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>0</v>
+      </c>
+      <c r="C806" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="D806" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E806" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="F806" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>15050</v>
+      </c>
+      <c r="C807" t="n">
+        <v>3</v>
+      </c>
+      <c r="D807" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E807" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F807"/>
+      <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18926,8 +18926,31 @@
       <c r="E807" t="n">
         <v>2.92000007629395</v>
       </c>
-      <c r="F807"/>
+      <c r="F807" t="n">
+        <v>2.98000001907349</v>
+      </c>
       <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C808" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D808" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E808" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F808"/>
+      <c r="G808" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18949,8 +18949,31 @@
       <c r="E808" t="n">
         <v>2.92000007629395</v>
       </c>
-      <c r="F808"/>
+      <c r="F808" t="n">
+        <v>2.90000009536743</v>
+      </c>
       <c r="G808" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B809" t="n">
+        <v>2450</v>
+      </c>
+      <c r="C809" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="D809" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="E809" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="F809"/>
+      <c r="G809" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -18979,6 +18979,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B810" t="n">
+        <v>350</v>
+      </c>
+      <c r="C810" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E810" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F810" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G810" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -19002,6 +19002,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B811" t="n">
+        <v>0</v>
+      </c>
+      <c r="C811" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D811" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E811" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F811" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G811" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -21513,6 +21513,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B814" t="n">
+        <v>700</v>
+      </c>
+      <c r="C814" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D814" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="E814" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F814" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G814" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H814" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -23984,6 +23984,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" t="s">
+        <v>9</v>
+      </c>
+      <c r="B815" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C815" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D815" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E815" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F815" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G815" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H815" t="n">
+        <v>0</v>
+      </c>
+      <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -24013,6 +24013,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" t="s">
+        <v>9</v>
+      </c>
+      <c r="B816" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C816" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D816" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E816" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F816" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G816" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H816" t="n">
+        <v>0</v>
+      </c>
+      <c r="I816" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -24042,6 +24042,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="s">
+        <v>9</v>
+      </c>
+      <c r="B817" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C817" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D817" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E817" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F817" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G817" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H817" t="n">
+        <v>0</v>
+      </c>
+      <c r="I817" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="s">
+        <v>9</v>
+      </c>
+      <c r="B818" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C818" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D818" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E818" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F818" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G818" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H818" t="n">
+        <v>700</v>
+      </c>
+      <c r="I818" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -24100,6 +24100,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" t="s">
+        <v>9</v>
+      </c>
+      <c r="B819" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C819" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D819" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E819" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F819" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G819" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H819" t="n">
+        <v>0</v>
+      </c>
+      <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -24129,6 +24129,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" t="s">
+        <v>9</v>
+      </c>
+      <c r="B820" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C820" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D820" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E820" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F820" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G820" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H820" t="n">
+        <v>0</v>
+      </c>
+      <c r="I820" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="s">
+        <v>9</v>
+      </c>
+      <c r="B821" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C821" t="n">
+        <v>3</v>
+      </c>
+      <c r="D821" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="E821" t="n">
+        <v>3</v>
+      </c>
+      <c r="F821" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G821" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H821" t="n">
+        <v>98350</v>
+      </c>
+      <c r="I821" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -24187,6 +24187,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="s">
+        <v>9</v>
+      </c>
+      <c r="B822" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C822" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="D822" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="E822" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="F822" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="G822" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="H822" t="n">
+        <v>92750</v>
+      </c>
+      <c r="I822" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -24216,6 +24216,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="823">
+      <c r="A823" t="s">
+        <v>9</v>
+      </c>
+      <c r="B823" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C823" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="D823" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E823" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="F823" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="G823" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="H823" t="n">
+        <v>48300</v>
+      </c>
+      <c r="I823" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNE.MI.xlsx
+++ b/data/VNE.MI.xlsx
@@ -24245,6 +24245,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="824">
+      <c r="A824" t="s">
+        <v>9</v>
+      </c>
+      <c r="B824" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C824" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="D824" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="E824" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F824" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="G824" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="H824" t="n">
+        <v>54250</v>
+      </c>
+      <c r="I824" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
